--- a/教育（きょういく）.xlsx
+++ b/教育（きょういく）.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\苗欣奕的东西\折跃\Japanese\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{897FC42E-C50A-43EC-8219-253CC16AD00A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{181A414F-4D66-48B0-BC0F-9B837AE9A7F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="教育（きょういく）" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="282">
   <si>
     <t>教育</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1187,6 +1187,14 @@
   </si>
   <si>
     <t>はかせ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>解釈</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>かいしゃ</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2409,7 +2417,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16A7530C-A037-4E3F-BEDC-CDFEDA1B5E82}">
-  <dimension ref="A2:B3"/>
+  <dimension ref="A2:B4"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.6640625" bestFit="1" customWidth="1"/>
@@ -2429,6 +2437,14 @@
       </c>
       <c r="B3" s="1" t="s">
         <v>196</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="18" x14ac:dyDescent="0.45">
+      <c r="A4" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>281</v>
       </c>
     </row>
   </sheetData>
